--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="131">
   <si>
     <t>int</t>
   </si>
@@ -167,16 +167,16 @@
     <t>prefab</t>
   </si>
   <si>
-    <t>GameEndPanel</t>
+    <t>EndPanel</t>
   </si>
   <si>
     <t>结束面板</t>
   </si>
   <si>
-    <t>UI/Panel/GameEndPanel</t>
-  </si>
-  <si>
-    <t>ArtRes/UI/Panel/GameEndPanel</t>
+    <t>UI/Panel/EndPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/EndPanel</t>
   </si>
   <si>
     <t>GameUIPanel</t>
@@ -191,16 +191,16 @@
     <t>ArtRes/UI/Panel/GameUIPanel</t>
   </si>
   <si>
-    <t>LevelPassPanel</t>
-  </si>
-  <si>
-    <t>通关面板</t>
-  </si>
-  <si>
-    <t>UI/Panel/LevelPassPanel</t>
-  </si>
-  <si>
-    <t>ArtRes/UI/Panel/LevelPassPanel</t>
+    <t>PausePanel</t>
+  </si>
+  <si>
+    <t>暂停面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/PausePanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/PausePanel</t>
   </si>
   <si>
     <t>GrayPanel</t>
@@ -215,16 +215,40 @@
     <t>ArtRes/UI/Panel/GrayPanel</t>
   </si>
   <si>
-    <t>PopupPanel</t>
-  </si>
-  <si>
-    <t>弹出面板</t>
-  </si>
-  <si>
-    <t>UI/Panel/PopupPanel</t>
-  </si>
-  <si>
-    <t>ArtRes/UI/Panel/PopupPanel</t>
+    <t>GameOverPanel</t>
+  </si>
+  <si>
+    <t>游戏失败面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/GameOverPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/GameOverPanel</t>
+  </si>
+  <si>
+    <t>FaderPanel</t>
+  </si>
+  <si>
+    <t>淡入面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/FaderPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/FaderPanel</t>
+  </si>
+  <si>
+    <t>SettingPanel</t>
+  </si>
+  <si>
+    <t>设置面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/SettingPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/SettingPanel</t>
   </si>
   <si>
     <t>卡牌1</t>
@@ -1543,7 +1567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
@@ -1896,44 +1920,44 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
-        <v>10001</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>10002</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>71</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s">
         <v>72</v>
@@ -1942,18 +1966,18 @@
         <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
         <v>74</v>
@@ -1968,348 +1992,400 @@
         <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" t="s">
         <v>78</v>
-      </c>
-      <c r="F28" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" t="s">
-        <v>69</v>
-      </c>
-      <c r="H28" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
-        <v>10009</v>
+        <v>10007</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
-        <v>10010</v>
+        <v>10008</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G34" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
-        <v>10011</v>
+        <v>10009</v>
       </c>
       <c r="B35">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
-        <v>10012</v>
+        <v>10010</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G36" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
-        <v>10013</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
+        <v>10011</v>
+      </c>
+      <c r="B37">
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G37" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
-        <v>20001</v>
-      </c>
-      <c r="B38" t="s">
-        <v>107</v>
+        <v>10012</v>
+      </c>
+      <c r="B38">
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G38" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
-        <v>30001</v>
+        <v>10013</v>
       </c>
       <c r="B39" t="s">
         <v>112</v>
       </c>
       <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
         <v>113</v>
       </c>
-      <c r="D39">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>114</v>
       </c>
-      <c r="F39" t="s">
-        <v>115</v>
-      </c>
       <c r="G39" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
+        <v>20001</v>
+      </c>
+      <c r="B40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" t="s">
+        <v>119</v>
+      </c>
+      <c r="H40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>30001</v>
+      </c>
+      <c r="B41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41" t="s">
+        <v>123</v>
+      </c>
+      <c r="G41" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
         <v>40001</v>
       </c>
-      <c r="B40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40">
+      <c r="B42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42">
         <v>1</v>
       </c>
-      <c r="E40" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" t="s">
-        <v>120</v>
-      </c>
-      <c r="G40" t="s">
-        <v>121</v>
-      </c>
-      <c r="H40" t="s">
-        <v>122</v>
+      <c r="E42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" t="s">
+        <v>128</v>
+      </c>
+      <c r="G42" t="s">
+        <v>129</v>
+      </c>
+      <c r="H42" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="188">
   <si>
     <t>int</t>
   </si>
@@ -251,127 +251,298 @@
     <t>ArtRes/UI/Panel/SettingPanel</t>
   </si>
   <si>
-    <t>卡牌1</t>
-  </si>
-  <si>
-    <t>Materials/1</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/1</t>
-  </si>
-  <si>
-    <t>materials</t>
-  </si>
-  <si>
-    <t>mat</t>
-  </si>
-  <si>
-    <t>卡牌2</t>
-  </si>
-  <si>
-    <t>Materials/2</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/2</t>
-  </si>
-  <si>
-    <t>卡牌3</t>
-  </si>
-  <si>
-    <t>Materials/3</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/3</t>
-  </si>
-  <si>
-    <t>卡牌4</t>
-  </si>
-  <si>
-    <t>Materials/4</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/4</t>
-  </si>
-  <si>
-    <t>卡牌5</t>
-  </si>
-  <si>
-    <t>Materials/5</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/5</t>
-  </si>
-  <si>
-    <t>卡牌6</t>
-  </si>
-  <si>
-    <t>Materials/6</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/6</t>
-  </si>
-  <si>
-    <t>卡牌7</t>
-  </si>
-  <si>
-    <t>Materials/7</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/7</t>
-  </si>
-  <si>
-    <t>卡牌8</t>
-  </si>
-  <si>
-    <t>Materials/8</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/8</t>
-  </si>
-  <si>
-    <t>卡牌9</t>
-  </si>
-  <si>
-    <t>Materials/9</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/9</t>
-  </si>
-  <si>
-    <t>卡牌10</t>
-  </si>
-  <si>
-    <t>Materials/10</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/10</t>
-  </si>
-  <si>
-    <t>卡牌11</t>
-  </si>
-  <si>
-    <t>Materials/11</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/11</t>
-  </si>
-  <si>
-    <t>卡牌12</t>
-  </si>
-  <si>
-    <t>Materials/12</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/12</t>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>Materials/BG</t>
-  </si>
-  <si>
-    <t>ArtRes/Materials/BG</t>
+    <t>Ball</t>
+  </si>
+  <si>
+    <t>没戴面具的球</t>
+  </si>
+  <si>
+    <t>Sprites/Ball</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Ball</t>
+  </si>
+  <si>
+    <t>sprites</t>
+  </si>
+  <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>Ball1</t>
+  </si>
+  <si>
+    <t>戴面具的球</t>
+  </si>
+  <si>
+    <t>Sprites/Ball1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Ball1</t>
+  </si>
+  <si>
+    <t>Cassette</t>
+  </si>
+  <si>
+    <t>没戴面具的磁带</t>
+  </si>
+  <si>
+    <t>Sprites/Cassette</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Cassette</t>
+  </si>
+  <si>
+    <t>Cassette1</t>
+  </si>
+  <si>
+    <t>戴面具的磁带</t>
+  </si>
+  <si>
+    <t>Sprites/Cassette1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Cassette1</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>没戴面具的巧克力</t>
+  </si>
+  <si>
+    <t>Sprites/Chocolate</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Chocolate</t>
+  </si>
+  <si>
+    <t>Chocolate1</t>
+  </si>
+  <si>
+    <t>戴面具的巧克力</t>
+  </si>
+  <si>
+    <t>Sprites/Chocolate1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Chocolate1</t>
+  </si>
+  <si>
+    <t>Crocodile</t>
+  </si>
+  <si>
+    <t>没戴面具的鳄鱼</t>
+  </si>
+  <si>
+    <t>Sprites/Crocodile</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Crocodile</t>
+  </si>
+  <si>
+    <t>Crocodile1</t>
+  </si>
+  <si>
+    <t>戴面具的鳄鱼</t>
+  </si>
+  <si>
+    <t>Sprites/Crocodile1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Crocodile1</t>
+  </si>
+  <si>
+    <t>Crow</t>
+  </si>
+  <si>
+    <t>没戴面具的乌鸦</t>
+  </si>
+  <si>
+    <t>Sprites/Crow</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Crow</t>
+  </si>
+  <si>
+    <t>Crow1</t>
+  </si>
+  <si>
+    <t>戴面具的乌鸦</t>
+  </si>
+  <si>
+    <t>Sprites/Crow1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Crow1</t>
+  </si>
+  <si>
+    <t>Elephant</t>
+  </si>
+  <si>
+    <t>没戴面具的大象</t>
+  </si>
+  <si>
+    <t>Sprites/Elephant</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Elephant</t>
+  </si>
+  <si>
+    <t>Elephant1</t>
+  </si>
+  <si>
+    <t>戴面具的大象</t>
+  </si>
+  <si>
+    <t>Sprites/Elephant1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Elephant1</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>面具本体</t>
+  </si>
+  <si>
+    <t>Sprites/Mask</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Mask</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>没戴面具的老鼠</t>
+  </si>
+  <si>
+    <t>Sprites/Mouse</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Mouse</t>
+  </si>
+  <si>
+    <t>Mouse1</t>
+  </si>
+  <si>
+    <t>戴面具的老鼠</t>
+  </si>
+  <si>
+    <t>Sprites/Mouse1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Mouse1</t>
+  </si>
+  <si>
+    <t>Rock</t>
+  </si>
+  <si>
+    <t>没戴面具的岩石</t>
+  </si>
+  <si>
+    <t>Sprites/Rock</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Rock</t>
+  </si>
+  <si>
+    <t>Rock1</t>
+  </si>
+  <si>
+    <t>戴面具的岩石</t>
+  </si>
+  <si>
+    <t>Sprites/Rock1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Rock1</t>
+  </si>
+  <si>
+    <t>Streetlight</t>
+  </si>
+  <si>
+    <t>没戴面具的路灯</t>
+  </si>
+  <si>
+    <t>Sprites/Streetlight</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Streetlight</t>
+  </si>
+  <si>
+    <t>Streetlight1</t>
+  </si>
+  <si>
+    <t>戴面具的路灯</t>
+  </si>
+  <si>
+    <t>Sprites/Streetlight1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Streetlight1</t>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>没戴面具的狼</t>
+  </si>
+  <si>
+    <t>Sprites/Wolf</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Wolf</t>
+  </si>
+  <si>
+    <t>Wolf1</t>
+  </si>
+  <si>
+    <t>戴面具的狼</t>
+  </si>
+  <si>
+    <t>Sprites/Wolf1</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Wolf1</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>栅栏</t>
+  </si>
+  <si>
+    <t>Sprites/Fence</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Fence</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>人</t>
+  </si>
+  <si>
+    <t>Sprites/Human</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Human</t>
+  </si>
+  <si>
+    <t>Swamp</t>
+  </si>
+  <si>
+    <t>沼泽</t>
+  </si>
+  <si>
+    <t>Sprites/Swamp</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/Swamp</t>
   </si>
   <si>
     <t>Card</t>
@@ -1567,7 +1738,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
@@ -1575,7 +1746,7 @@
     <col min="4" max="4" width="16.9907407407407" customWidth="1"/>
     <col min="5" max="5" width="28.212962962963" customWidth="1"/>
     <col min="6" max="6" width="32.3611111111111" customWidth="1"/>
-    <col min="7" max="7" width="37.6574074074074" customWidth="1"/>
+    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
     <col min="8" max="8" width="15.6666666666667" customWidth="1"/>
     <col min="9" max="9" width="13.6111111111111" customWidth="1"/>
     <col min="10" max="10" width="15.8518518518519" customWidth="1"/>
@@ -1976,312 +2147,312 @@
       <c r="A27">
         <v>10001</v>
       </c>
-      <c r="B27">
-        <v>1</v>
+      <c r="B27" t="s">
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
         <v>10002</v>
       </c>
-      <c r="B28">
-        <v>2</v>
+      <c r="B28" t="s">
+        <v>80</v>
       </c>
       <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s">
         <v>79</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="E28" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
         <v>10003</v>
       </c>
-      <c r="B29">
-        <v>3</v>
+      <c r="B29" t="s">
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
         <v>10004</v>
       </c>
-      <c r="B30">
-        <v>4</v>
+      <c r="B30" t="s">
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
         <v>10005</v>
       </c>
-      <c r="B31">
-        <v>5</v>
+      <c r="B31" t="s">
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
         <v>10006</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32">
         <v>6</v>
       </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32">
-        <v>4</v>
-      </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
         <v>10007</v>
       </c>
-      <c r="B33">
-        <v>7</v>
+      <c r="B33" t="s">
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
         <v>10008</v>
       </c>
-      <c r="B34">
-        <v>8</v>
+      <c r="B34" t="s">
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
         <v>10009</v>
       </c>
-      <c r="B35">
-        <v>9</v>
+      <c r="B35" t="s">
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F35" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
         <v>10010</v>
       </c>
-      <c r="B36">
-        <v>10</v>
+      <c r="B36" t="s">
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
         <v>10011</v>
       </c>
-      <c r="B37">
-        <v>11</v>
+      <c r="B37" t="s">
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
         <v>10012</v>
       </c>
-      <c r="B38">
-        <v>12</v>
+      <c r="B38" t="s">
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F38" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:8">
@@ -2289,103 +2460,389 @@
         <v>10013</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F39" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:8">
+      <c r="A40">
+        <v>10014</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>130</v>
+      </c>
+      <c r="F40" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40">
+      <c r="H40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:8">
+      <c r="A41">
+        <v>10015</v>
+      </c>
+      <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" t="s">
+        <v>135</v>
+      </c>
+      <c r="G41" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:8">
+      <c r="A42">
+        <v>10016</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G42" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:8">
+      <c r="A43">
+        <v>10017</v>
+      </c>
+      <c r="B43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G43" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:8">
+      <c r="A44">
+        <v>10018</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:8">
+      <c r="A45">
+        <v>10019</v>
+      </c>
+      <c r="B45" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" t="s">
+        <v>149</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:8">
+      <c r="A46">
+        <v>10020</v>
+      </c>
+      <c r="B46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46" t="s">
+        <v>154</v>
+      </c>
+      <c r="F46" t="s">
+        <v>155</v>
+      </c>
+      <c r="G46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:8">
+      <c r="A47">
+        <v>10021</v>
+      </c>
+      <c r="B47" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47" t="s">
+        <v>158</v>
+      </c>
+      <c r="F47" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:8">
+      <c r="A48">
+        <v>10022</v>
+      </c>
+      <c r="B48" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+      <c r="E48" t="s">
+        <v>162</v>
+      </c>
+      <c r="F48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:8">
+      <c r="A49">
+        <v>10023</v>
+      </c>
+      <c r="B49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49" t="s">
+        <v>165</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>166</v>
+      </c>
+      <c r="F49" t="s">
+        <v>167</v>
+      </c>
+      <c r="G49" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:8">
+      <c r="A50">
+        <v>10024</v>
+      </c>
+      <c r="B50" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="E50" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" t="s">
+        <v>171</v>
+      </c>
+      <c r="G50" t="s">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
         <v>20001</v>
       </c>
-      <c r="B40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40">
+      <c r="B51" t="s">
+        <v>172</v>
+      </c>
+      <c r="C51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51">
         <v>0</v>
       </c>
-      <c r="E40" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" t="s">
-        <v>118</v>
-      </c>
-      <c r="G40" t="s">
-        <v>119</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="E51" t="s">
+        <v>174</v>
+      </c>
+      <c r="F51" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+    <row r="52" spans="1:8">
+      <c r="A52">
         <v>30001</v>
       </c>
-      <c r="B41" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41">
+      <c r="B52" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52">
         <v>10</v>
       </c>
-      <c r="E41" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" t="s">
-        <v>123</v>
-      </c>
-      <c r="G41" t="s">
-        <v>124</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="E52" t="s">
+        <v>179</v>
+      </c>
+      <c r="F52" t="s">
+        <v>180</v>
+      </c>
+      <c r="G52" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42">
+    <row r="53" spans="1:8">
+      <c r="A53">
         <v>40001</v>
       </c>
-      <c r="B42" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42">
+      <c r="B53" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53">
         <v>1</v>
       </c>
-      <c r="E42" t="s">
-        <v>127</v>
-      </c>
-      <c r="F42" t="s">
-        <v>128</v>
-      </c>
-      <c r="G42" t="s">
-        <v>129</v>
-      </c>
-      <c r="H42" t="s">
-        <v>130</v>
+      <c r="E53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F53" t="s">
+        <v>185</v>
+      </c>
+      <c r="G53" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="15180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="236">
   <si>
     <t>int</t>
   </si>
@@ -575,22 +575,166 @@
     <t>vfx</t>
   </si>
   <si>
-    <t>BGM</t>
-  </si>
-  <si>
-    <t>背景音乐</t>
-  </si>
-  <si>
-    <t>Music/BGM</t>
-  </si>
-  <si>
-    <t>ArtRes/Music/BGM</t>
+    <t>主界面</t>
+  </si>
+  <si>
+    <t>开始面板播放音效</t>
+  </si>
+  <si>
+    <t>Music/主界面</t>
+  </si>
+  <si>
+    <t>ArtRes/Music/主界面</t>
   </si>
   <si>
     <t>music</t>
   </si>
   <si>
+    <t>mp3</t>
+  </si>
+  <si>
+    <t>失败界面</t>
+  </si>
+  <si>
+    <t>失败面板播放的音效</t>
+  </si>
+  <si>
+    <t>Music/失败界面</t>
+  </si>
+  <si>
+    <t>ArtRes/Music/失败界面</t>
+  </si>
+  <si>
     <t>wav</t>
+  </si>
+  <si>
+    <t>游玩界面</t>
+  </si>
+  <si>
+    <t>游戏场景播放音效</t>
+  </si>
+  <si>
+    <t>Music/游玩界面</t>
+  </si>
+  <si>
+    <t>ArtRes/Music/游玩界面</t>
+  </si>
+  <si>
+    <t>通关界面</t>
+  </si>
+  <si>
+    <t>游戏胜利播放音效</t>
+  </si>
+  <si>
+    <t>Music/通关界面</t>
+  </si>
+  <si>
+    <t>ArtRes/Music/通关界面</t>
+  </si>
+  <si>
+    <t>里世界白噪声</t>
+  </si>
+  <si>
+    <t>切换到里世界的背景音乐</t>
+  </si>
+  <si>
+    <t>Music/里世界白噪声</t>
+  </si>
+  <si>
+    <t>ArtRes/Music/里世界白噪声</t>
+  </si>
+  <si>
+    <t>灯附身音效</t>
+  </si>
+  <si>
+    <t>Sound/灯附身音效</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/灯附身音效</t>
+  </si>
+  <si>
+    <t>sound</t>
+  </si>
+  <si>
+    <t>摁键选项</t>
+  </si>
+  <si>
+    <t>Sound/摁键选项</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/摁键选项</t>
+  </si>
+  <si>
+    <t>附身磁带</t>
+  </si>
+  <si>
+    <t>Sound/附身磁带</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/附身磁带</t>
+  </si>
+  <si>
+    <t>附身交互音效</t>
+  </si>
+  <si>
+    <t>Sound/附身交互音效</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/附身交互音效</t>
+  </si>
+  <si>
+    <t>狼附身时音效</t>
+  </si>
+  <si>
+    <t>Sound/狼附身时音效</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/狼附身时音效</t>
+  </si>
+  <si>
+    <t>狼移动音效</t>
+  </si>
+  <si>
+    <t>Sound/狼移动音效</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/狼移动音效</t>
+  </si>
+  <si>
+    <t>老鼠移动音效</t>
+  </si>
+  <si>
+    <t>Sound/老鼠移动音效</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/老鼠移动音效</t>
+  </si>
+  <si>
+    <t>游戏开始摁键</t>
+  </si>
+  <si>
+    <t>Sound/游戏开始摁键</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/游戏开始摁键</t>
+  </si>
+  <si>
+    <t>游戏失败音效</t>
+  </si>
+  <si>
+    <t>Sound/游戏失败音效</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/游戏失败音效</t>
+  </si>
+  <si>
+    <t>游戏失败音效02</t>
+  </si>
+  <si>
+    <t>Sound/游戏失败音效02</t>
+  </si>
+  <si>
+    <t>ArtRes/Sound/游戏失败音效02</t>
   </si>
 </sst>
 </file>
@@ -1738,18 +1882,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K53"/>
-  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K67"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
-    <col min="2" max="3" width="17.3055555555556" customWidth="1"/>
-    <col min="4" max="4" width="16.9907407407407" customWidth="1"/>
-    <col min="5" max="5" width="28.212962962963" customWidth="1"/>
-    <col min="6" max="6" width="32.3611111111111" customWidth="1"/>
-    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
-    <col min="8" max="8" width="15.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="13.6111111111111" customWidth="1"/>
-    <col min="10" max="10" width="15.8518518518519" customWidth="1"/>
+    <col min="1" max="1" width="12.1730769230769" customWidth="1"/>
+    <col min="2" max="2" width="17.3076923076923" customWidth="1"/>
+    <col min="3" max="3" width="24.0384615384615" customWidth="1"/>
+    <col min="4" max="4" width="16.9903846153846" customWidth="1"/>
+    <col min="5" max="5" width="28.2115384615385" customWidth="1"/>
+    <col min="6" max="6" width="32.3653846153846" customWidth="1"/>
+    <col min="7" max="7" width="26.4423076923077" customWidth="1"/>
+    <col min="8" max="8" width="15.6634615384615" customWidth="1"/>
+    <col min="9" max="9" width="13.6153846153846" customWidth="1"/>
+    <col min="10" max="10" width="15.8557692307692" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2845,6 +2990,370 @@
         <v>187</v>
       </c>
     </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>40002</v>
+      </c>
+      <c r="B54" t="s">
+        <v>188</v>
+      </c>
+      <c r="C54" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" t="s">
+        <v>190</v>
+      </c>
+      <c r="F54" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>40003</v>
+      </c>
+      <c r="B55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>195</v>
+      </c>
+      <c r="F55" t="s">
+        <v>196</v>
+      </c>
+      <c r="G55" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>40004</v>
+      </c>
+      <c r="B56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" t="s">
+        <v>200</v>
+      </c>
+      <c r="G56" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>40005</v>
+      </c>
+      <c r="B57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>203</v>
+      </c>
+      <c r="F57" t="s">
+        <v>204</v>
+      </c>
+      <c r="G57" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>40006</v>
+      </c>
+      <c r="B58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>206</v>
+      </c>
+      <c r="F58" t="s">
+        <v>207</v>
+      </c>
+      <c r="G58" t="s">
+        <v>208</v>
+      </c>
+      <c r="H58" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>40007</v>
+      </c>
+      <c r="B59" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" t="s">
+        <v>209</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F59" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" t="s">
+        <v>208</v>
+      </c>
+      <c r="H59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>40008</v>
+      </c>
+      <c r="B60" t="s">
+        <v>212</v>
+      </c>
+      <c r="C60" t="s">
+        <v>212</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>213</v>
+      </c>
+      <c r="F60" t="s">
+        <v>214</v>
+      </c>
+      <c r="G60" t="s">
+        <v>208</v>
+      </c>
+      <c r="H60" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>40009</v>
+      </c>
+      <c r="B61" t="s">
+        <v>215</v>
+      </c>
+      <c r="C61" t="s">
+        <v>215</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>216</v>
+      </c>
+      <c r="F61" t="s">
+        <v>217</v>
+      </c>
+      <c r="G61" t="s">
+        <v>208</v>
+      </c>
+      <c r="H61" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>40010</v>
+      </c>
+      <c r="B62" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" t="s">
+        <v>218</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>219</v>
+      </c>
+      <c r="F62" t="s">
+        <v>220</v>
+      </c>
+      <c r="G62" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>40011</v>
+      </c>
+      <c r="B63" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" t="s">
+        <v>221</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>222</v>
+      </c>
+      <c r="F63" t="s">
+        <v>223</v>
+      </c>
+      <c r="G63" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>40012</v>
+      </c>
+      <c r="B64" t="s">
+        <v>224</v>
+      </c>
+      <c r="C64" t="s">
+        <v>224</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>225</v>
+      </c>
+      <c r="F64" t="s">
+        <v>226</v>
+      </c>
+      <c r="G64" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>40013</v>
+      </c>
+      <c r="B65" t="s">
+        <v>227</v>
+      </c>
+      <c r="C65" t="s">
+        <v>227</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>228</v>
+      </c>
+      <c r="F65" t="s">
+        <v>229</v>
+      </c>
+      <c r="G65" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>40014</v>
+      </c>
+      <c r="B66" t="s">
+        <v>230</v>
+      </c>
+      <c r="C66" t="s">
+        <v>230</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>231</v>
+      </c>
+      <c r="F66" t="s">
+        <v>232</v>
+      </c>
+      <c r="G66" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>40015</v>
+      </c>
+      <c r="B67" t="s">
+        <v>233</v>
+      </c>
+      <c r="C67" t="s">
+        <v>233</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>234</v>
+      </c>
+      <c r="F67" t="s">
+        <v>235</v>
+      </c>
+      <c r="G67" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15180"/>
+    <workbookView windowHeight="15000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="244">
   <si>
     <t>int</t>
   </si>
@@ -545,16 +545,40 @@
     <t>ArtRes/Sprites/Swamp</t>
   </si>
   <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>卡牌预制体</t>
-  </si>
-  <si>
-    <t>Prefabs/Card</t>
-  </si>
-  <si>
-    <t>ArtRes/Prefabs/Card</t>
+    <t>SoulPlayer</t>
+  </si>
+  <si>
+    <t>里世界会出现在人物头顶的图标</t>
+  </si>
+  <si>
+    <t>Sprites/SoulPlayer</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/SoulPlayer</t>
+  </si>
+  <si>
+    <t>SoulOther</t>
+  </si>
+  <si>
+    <t>里世界会出现在其他动物或者物品头顶的图标</t>
+  </si>
+  <si>
+    <t>Sprites/SoulOther</t>
+  </si>
+  <si>
+    <t>ArtRes/Sprites/SoulOther</t>
+  </si>
+  <si>
+    <t>MousePrefab</t>
+  </si>
+  <si>
+    <t>老鼠预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/MousePrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/MousePrefab</t>
   </si>
   <si>
     <t>prefabs</t>
@@ -747,10 +771,23 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1220,141 +1257,162 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1882,12 +1940,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12.1730769230769" customWidth="1"/>
     <col min="2" max="2" width="17.3076923076923" customWidth="1"/>
-    <col min="3" max="3" width="24.0384615384615" customWidth="1"/>
+    <col min="3" max="3" width="24.0384615384615" style="3" customWidth="1"/>
     <col min="4" max="4" width="16.9903846153846" customWidth="1"/>
     <col min="5" max="5" width="28.2115384615385" customWidth="1"/>
     <col min="6" max="6" width="32.3653846153846" customWidth="1"/>
@@ -1897,14 +1955,14 @@
     <col min="10" max="10" width="15.8557692307692" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" ht="17" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
@@ -1924,39 +1982,39 @@
       </c>
     </row>
     <row r="2" ht="101" customHeight="1" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" ht="17" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
@@ -1982,7 +2040,7 @@
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>1</v>
       </c>
       <c r="D4">
@@ -2010,14 +2068,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" ht="17" spans="1:11">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
@@ -2045,14 +2103,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" ht="17" spans="1:11">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D6" t="s">
@@ -2080,14 +2138,14 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" ht="17" spans="1:8">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D19">
@@ -2106,14 +2164,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" ht="17" spans="1:8">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20" t="s">
         <v>46</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D20">
@@ -2132,14 +2190,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:8">
+    <row r="21" customFormat="1" ht="17" spans="1:8">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D21">
@@ -2158,14 +2216,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:8">
+    <row r="22" customFormat="1" ht="17" spans="1:8">
       <c r="A22">
         <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D22">
@@ -2184,14 +2242,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:8">
+    <row r="23" customFormat="1" ht="17" spans="1:8">
       <c r="A23">
         <v>5</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D23">
@@ -2210,14 +2268,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:8">
+    <row r="24" customFormat="1" ht="17" spans="1:8">
       <c r="A24">
         <v>6</v>
       </c>
       <c r="B24" t="s">
         <v>62</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D24">
@@ -2236,14 +2294,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:8">
+    <row r="25" customFormat="1" ht="17" spans="1:8">
       <c r="A25">
         <v>7</v>
       </c>
       <c r="B25" t="s">
         <v>66</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D25">
@@ -2262,14 +2320,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:8">
+    <row r="26" customFormat="1" ht="17" spans="1:8">
       <c r="A26">
         <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>70</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D26">
@@ -2288,14 +2346,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" ht="17" spans="1:8">
       <c r="A27">
         <v>10001</v>
       </c>
       <c r="B27" t="s">
         <v>74</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D27">
@@ -2314,14 +2372,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:8">
+    <row r="28" customFormat="1" ht="17" spans="1:8">
       <c r="A28">
         <v>10002</v>
       </c>
       <c r="B28" t="s">
         <v>80</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D28">
@@ -2340,14 +2398,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:8">
+    <row r="29" customFormat="1" ht="17" spans="1:8">
       <c r="A29">
         <v>10003</v>
       </c>
       <c r="B29" t="s">
         <v>84</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D29">
@@ -2366,14 +2424,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="1:8">
+    <row r="30" customFormat="1" ht="17" spans="1:8">
       <c r="A30">
         <v>10004</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D30">
@@ -2392,14 +2450,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:8">
+    <row r="31" customFormat="1" ht="17" spans="1:8">
       <c r="A31">
         <v>10005</v>
       </c>
       <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D31">
@@ -2418,14 +2476,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:8">
+    <row r="32" customFormat="1" ht="17" spans="1:8">
       <c r="A32">
         <v>10006</v>
       </c>
       <c r="B32" t="s">
         <v>96</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>97</v>
       </c>
       <c r="D32">
@@ -2444,14 +2502,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:8">
+    <row r="33" customFormat="1" ht="17" spans="1:8">
       <c r="A33">
         <v>10007</v>
       </c>
       <c r="B33" t="s">
         <v>100</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>101</v>
       </c>
       <c r="D33">
@@ -2470,14 +2528,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:8">
+    <row r="34" customFormat="1" ht="17" spans="1:8">
       <c r="A34">
         <v>10008</v>
       </c>
       <c r="B34" t="s">
         <v>104</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>105</v>
       </c>
       <c r="D34">
@@ -2496,14 +2554,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:8">
+    <row r="35" customFormat="1" ht="17" spans="1:8">
       <c r="A35">
         <v>10009</v>
       </c>
       <c r="B35" t="s">
         <v>108</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>109</v>
       </c>
       <c r="D35">
@@ -2522,14 +2580,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:8">
+    <row r="36" customFormat="1" ht="17" spans="1:8">
       <c r="A36">
         <v>10010</v>
       </c>
       <c r="B36" t="s">
         <v>112</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>113</v>
       </c>
       <c r="D36">
@@ -2548,14 +2606,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" customFormat="1" spans="1:8">
+    <row r="37" customFormat="1" ht="17" spans="1:8">
       <c r="A37">
         <v>10011</v>
       </c>
       <c r="B37" t="s">
         <v>116</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D37">
@@ -2574,14 +2632,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:8">
+    <row r="38" customFormat="1" ht="17" spans="1:8">
       <c r="A38">
         <v>10012</v>
       </c>
       <c r="B38" t="s">
         <v>120</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D38">
@@ -2600,14 +2658,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:8">
+    <row r="39" customFormat="1" ht="17" spans="1:8">
       <c r="A39">
         <v>10013</v>
       </c>
       <c r="B39" t="s">
         <v>124</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D39">
@@ -2626,14 +2684,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:8">
+    <row r="40" customFormat="1" ht="17" spans="1:8">
       <c r="A40">
         <v>10014</v>
       </c>
       <c r="B40" t="s">
         <v>128</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D40">
@@ -2652,14 +2710,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" customFormat="1" spans="1:8">
+    <row r="41" customFormat="1" ht="17" spans="1:8">
       <c r="A41">
         <v>10015</v>
       </c>
       <c r="B41" t="s">
         <v>132</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D41">
@@ -2678,14 +2736,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:8">
+    <row r="42" customFormat="1" ht="17" spans="1:8">
       <c r="A42">
         <v>10016</v>
       </c>
       <c r="B42" t="s">
         <v>136</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D42">
@@ -2704,14 +2762,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" customFormat="1" spans="1:8">
+    <row r="43" customFormat="1" ht="17" spans="1:8">
       <c r="A43">
         <v>10017</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D43">
@@ -2730,14 +2788,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="1:8">
+    <row r="44" customFormat="1" ht="17" spans="1:8">
       <c r="A44">
         <v>10018</v>
       </c>
       <c r="B44" t="s">
         <v>144</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D44">
@@ -2756,14 +2814,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:8">
+    <row r="45" customFormat="1" ht="17" spans="1:8">
       <c r="A45">
         <v>10019</v>
       </c>
       <c r="B45" t="s">
         <v>148</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="3" t="s">
         <v>149</v>
       </c>
       <c r="D45">
@@ -2782,14 +2840,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:8">
+    <row r="46" customFormat="1" ht="17" spans="1:8">
       <c r="A46">
         <v>10020</v>
       </c>
       <c r="B46" t="s">
         <v>152</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="3" t="s">
         <v>153</v>
       </c>
       <c r="D46">
@@ -2808,14 +2866,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="1:8">
+    <row r="47" customFormat="1" ht="17" spans="1:8">
       <c r="A47">
         <v>10021</v>
       </c>
       <c r="B47" t="s">
         <v>156</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D47">
@@ -2834,14 +2892,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" customFormat="1" spans="1:8">
+    <row r="48" customFormat="1" ht="17" spans="1:8">
       <c r="A48">
         <v>10022</v>
       </c>
       <c r="B48" t="s">
         <v>160</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D48">
@@ -2860,14 +2918,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" customFormat="1" spans="1:8">
+    <row r="49" customFormat="1" ht="17" spans="1:8">
       <c r="A49">
         <v>10023</v>
       </c>
       <c r="B49" t="s">
         <v>164</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="3" t="s">
         <v>165</v>
       </c>
       <c r="D49">
@@ -2886,14 +2944,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:8">
+    <row r="50" customFormat="1" ht="17" spans="1:8">
       <c r="A50">
         <v>10024</v>
       </c>
       <c r="B50" t="s">
         <v>168</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>169</v>
       </c>
       <c r="D50">
@@ -2912,18 +2970,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" s="1" customFormat="1" ht="34" spans="1:8">
       <c r="A51">
-        <v>20001</v>
+        <v>10025</v>
       </c>
       <c r="B51" t="s">
         <v>172</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
         <v>174</v>
@@ -2932,150 +2990,150 @@
         <v>175</v>
       </c>
       <c r="G51" t="s">
+        <v>78</v>
+      </c>
+      <c r="H51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="34" spans="1:8">
+      <c r="A52">
+        <v>10026</v>
+      </c>
+      <c r="B52" t="s">
         <v>176</v>
       </c>
-      <c r="H51" t="s">
+      <c r="C52" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>178</v>
+      </c>
+      <c r="F52" t="s">
+        <v>179</v>
+      </c>
+      <c r="G52" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="17" spans="1:8">
+      <c r="A53" s="2">
+        <v>20001</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52">
+    <row r="54" s="1" customFormat="1" ht="17" spans="1:8">
+      <c r="A54" s="1">
         <v>30001</v>
       </c>
-      <c r="B52" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52">
+      <c r="B54" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D54" s="1">
         <v>10</v>
       </c>
-      <c r="E52" t="s">
-        <v>179</v>
-      </c>
-      <c r="F52" t="s">
-        <v>180</v>
-      </c>
-      <c r="G52" t="s">
-        <v>181</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="E54" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53">
+    <row r="55" ht="17" spans="1:8">
+      <c r="A55">
         <v>40001</v>
       </c>
-      <c r="B53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C53" t="s">
-        <v>183</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>184</v>
-      </c>
-      <c r="F53" t="s">
-        <v>185</v>
-      </c>
-      <c r="G53" t="s">
-        <v>186</v>
-      </c>
-      <c r="H53" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54">
-        <v>40002</v>
-      </c>
-      <c r="B54" t="s">
-        <v>188</v>
-      </c>
-      <c r="C54" t="s">
-        <v>189</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="B55" t="s">
         <v>190</v>
       </c>
-      <c r="F54" t="s">
+      <c r="C55" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="G54" t="s">
-        <v>186</v>
-      </c>
-      <c r="H54" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55">
-        <v>40003</v>
-      </c>
-      <c r="B55" t="s">
-        <v>193</v>
-      </c>
-      <c r="C55" t="s">
-        <v>194</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
       <c r="E55" t="s">
+        <v>192</v>
+      </c>
+      <c r="F55" t="s">
+        <v>193</v>
+      </c>
+      <c r="G55" t="s">
+        <v>194</v>
+      </c>
+      <c r="H55" t="s">
         <v>195</v>
       </c>
-      <c r="F55" t="s">
+    </row>
+    <row r="56" ht="17" spans="1:8">
+      <c r="A56">
+        <v>40002</v>
+      </c>
+      <c r="B56" t="s">
         <v>196</v>
       </c>
-      <c r="G55" t="s">
-        <v>186</v>
-      </c>
-      <c r="H55" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56">
-        <v>40004</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="C56" t="s">
-        <v>198</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" t="s">
         <v>199</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
+        <v>194</v>
+      </c>
+      <c r="H56" t="s">
         <v>200</v>
       </c>
-      <c r="G56" t="s">
-        <v>186</v>
-      </c>
-      <c r="H56" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+    </row>
+    <row r="57" ht="17" spans="1:8">
       <c r="A57">
-        <v>40005</v>
+        <v>40003</v>
       </c>
       <c r="B57" t="s">
         <v>201</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="3" t="s">
         <v>202</v>
       </c>
       <c r="D57">
@@ -3088,270 +3146,322 @@
         <v>204</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H57" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" ht="17" spans="1:8">
       <c r="A58">
-        <v>40006</v>
+        <v>40004</v>
       </c>
       <c r="B58" t="s">
         <v>205</v>
       </c>
-      <c r="C58" t="s">
-        <v>205</v>
+      <c r="C58" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G58" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="H58" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" ht="34" spans="1:8">
       <c r="A59">
-        <v>40007</v>
+        <v>40005</v>
       </c>
       <c r="B59" t="s">
         <v>209</v>
       </c>
-      <c r="C59" t="s">
-        <v>209</v>
+      <c r="C59" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G59" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="H59" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" ht="17" spans="1:8">
       <c r="A60">
-        <v>40008</v>
+        <v>40006</v>
       </c>
       <c r="B60" t="s">
-        <v>212</v>
-      </c>
-      <c r="C60" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G60" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H60" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" ht="17" spans="1:8">
       <c r="A61">
-        <v>40009</v>
+        <v>40007</v>
       </c>
       <c r="B61" t="s">
-        <v>215</v>
-      </c>
-      <c r="C61" t="s">
-        <v>215</v>
+        <v>217</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
       <c r="E61" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" t="s">
+        <v>219</v>
+      </c>
+      <c r="G61" t="s">
         <v>216</v>
       </c>
-      <c r="F61" t="s">
-        <v>217</v>
-      </c>
-      <c r="G61" t="s">
-        <v>208</v>
-      </c>
       <c r="H61" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" ht="17" spans="1:8">
       <c r="A62">
-        <v>40010</v>
+        <v>40008</v>
       </c>
       <c r="B62" t="s">
-        <v>218</v>
-      </c>
-      <c r="C62" t="s">
-        <v>218</v>
+        <v>220</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F62" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G62" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H62" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" ht="17" spans="1:8">
       <c r="A63">
-        <v>40011</v>
+        <v>40009</v>
       </c>
       <c r="B63" t="s">
-        <v>221</v>
-      </c>
-      <c r="C63" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F63" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G63" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H63" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" ht="17" spans="1:8">
       <c r="A64">
-        <v>40012</v>
+        <v>40010</v>
       </c>
       <c r="B64" t="s">
-        <v>224</v>
-      </c>
-      <c r="C64" t="s">
-        <v>224</v>
+        <v>226</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G64" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H64" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" ht="17" spans="1:8">
       <c r="A65">
-        <v>40013</v>
+        <v>40011</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
-      </c>
-      <c r="C65" t="s">
-        <v>227</v>
+        <v>229</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F65" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G65" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H65" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" ht="17" spans="1:8">
       <c r="A66">
-        <v>40014</v>
+        <v>40012</v>
       </c>
       <c r="B66" t="s">
-        <v>230</v>
-      </c>
-      <c r="C66" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F66" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G66" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" ht="17" spans="1:8">
       <c r="A67">
-        <v>40015</v>
+        <v>40013</v>
       </c>
       <c r="B67" t="s">
-        <v>233</v>
-      </c>
-      <c r="C67" t="s">
-        <v>233</v>
+        <v>235</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G67" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="H67" t="s">
-        <v>192</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" ht="17" spans="1:8">
+      <c r="A68">
+        <v>40014</v>
+      </c>
+      <c r="B68" t="s">
+        <v>238</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>239</v>
+      </c>
+      <c r="F68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G68" t="s">
+        <v>216</v>
+      </c>
+      <c r="H68" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" ht="17" spans="1:8">
+      <c r="A69">
+        <v>40015</v>
+      </c>
+      <c r="B69" t="s">
+        <v>241</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>242</v>
+      </c>
+      <c r="F69" t="s">
+        <v>243</v>
+      </c>
+      <c r="G69" t="s">
+        <v>216</v>
+      </c>
+      <c r="H69" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15000"/>
+    <workbookView windowHeight="14940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14940"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="288">
   <si>
     <t>int</t>
   </si>
@@ -582,6 +582,138 @@
   </si>
   <si>
     <t>prefabs</t>
+  </si>
+  <si>
+    <t>CassettePrefab</t>
+  </si>
+  <si>
+    <t>磁带预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/CassettePrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/CassettePrefab</t>
+  </si>
+  <si>
+    <t>WolfPrefab</t>
+  </si>
+  <si>
+    <t>狼预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/WolfPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/WolfPrefab</t>
+  </si>
+  <si>
+    <t>CrowPrefab</t>
+  </si>
+  <si>
+    <t>乌鸦预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/CrowPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/CrowPrefab</t>
+  </si>
+  <si>
+    <t>CrocodilePrefab</t>
+  </si>
+  <si>
+    <t>鳄鱼预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/CrocodilePrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/CrocodilePrefab</t>
+  </si>
+  <si>
+    <t>ElephantPrefab</t>
+  </si>
+  <si>
+    <t>大象预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/ElephantPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/ElephantPrefab</t>
+  </si>
+  <si>
+    <t>ChocolatePrefab</t>
+  </si>
+  <si>
+    <t>巧克力预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/ChocolatePrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/ChocolatePrefab</t>
+  </si>
+  <si>
+    <t>RockPrefab</t>
+  </si>
+  <si>
+    <t>岩石预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/RockPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/RockPrefab</t>
+  </si>
+  <si>
+    <t>StreetlightPrefab</t>
+  </si>
+  <si>
+    <t>路灯预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/StreetlightPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/StreetlightPrefab</t>
+  </si>
+  <si>
+    <t>BallPrefab</t>
+  </si>
+  <si>
+    <t>皮球预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/BallPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/BallPrefab</t>
+  </si>
+  <si>
+    <t>EmptyPrefab</t>
+  </si>
+  <si>
+    <t>空预制体，用来占位</t>
+  </si>
+  <si>
+    <t>Prefabs/EmptyPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/EmptyPrefab</t>
+  </si>
+  <si>
+    <t>HumanPrefab</t>
+  </si>
+  <si>
+    <t>人预制体</t>
+  </si>
+  <si>
+    <t>Prefabs/HumanPrefab</t>
+  </si>
+  <si>
+    <t>ArtRes/Prefabs/HumanPrefab</t>
   </si>
   <si>
     <t>Success</t>
@@ -1387,7 +1519,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1400,17 +1532,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1940,22 +2063,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K69"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:K80"/>
+  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1730769230769" customWidth="1"/>
-    <col min="2" max="2" width="17.3076923076923" customWidth="1"/>
-    <col min="3" max="3" width="24.0384615384615" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.9903846153846" customWidth="1"/>
-    <col min="5" max="5" width="28.2115384615385" customWidth="1"/>
-    <col min="6" max="6" width="32.3653846153846" customWidth="1"/>
-    <col min="7" max="7" width="26.4423076923077" customWidth="1"/>
-    <col min="8" max="8" width="15.6634615384615" customWidth="1"/>
-    <col min="9" max="9" width="13.6153846153846" customWidth="1"/>
-    <col min="10" max="10" width="15.8557692307692" customWidth="1"/>
+    <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
+    <col min="2" max="2" width="17.3055555555556" customWidth="1"/>
+    <col min="3" max="3" width="24.037037037037" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.9907407407407" customWidth="1"/>
+    <col min="5" max="5" width="28.212962962963" customWidth="1"/>
+    <col min="6" max="6" width="32.3611111111111" customWidth="1"/>
+    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="15.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="13.6111111111111" customWidth="1"/>
+    <col min="10" max="10" width="15.8518518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1982,7 +2105,7 @@
       </c>
     </row>
     <row r="2" ht="101" customHeight="1" spans="1:11">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -1994,20 +2117,20 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:11">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2068,7 +2191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:11">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2103,7 +2226,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:11">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2138,7 +2261,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:8">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2164,7 +2287,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" ht="17" spans="1:8">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2190,7 +2313,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="17" spans="1:8">
+    <row r="21" customFormat="1" spans="1:8">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2216,7 +2339,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="17" spans="1:8">
+    <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
         <v>4</v>
       </c>
@@ -2242,7 +2365,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="17" spans="1:8">
+    <row r="23" customFormat="1" spans="1:8">
       <c r="A23">
         <v>5</v>
       </c>
@@ -2268,7 +2391,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customFormat="1" ht="17" spans="1:8">
+    <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
         <v>6</v>
       </c>
@@ -2294,7 +2417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="17" spans="1:8">
+    <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
         <v>7</v>
       </c>
@@ -2320,7 +2443,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="17" spans="1:8">
+    <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
         <v>8</v>
       </c>
@@ -2346,7 +2469,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" ht="17" spans="1:8">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>10001</v>
       </c>
@@ -2372,7 +2495,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" customFormat="1" ht="17" spans="1:8">
+    <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
         <v>10002</v>
       </c>
@@ -2398,7 +2521,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" customFormat="1" ht="17" spans="1:8">
+    <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
         <v>10003</v>
       </c>
@@ -2424,7 +2547,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="1" ht="17" spans="1:8">
+    <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
         <v>10004</v>
       </c>
@@ -2450,7 +2573,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" customFormat="1" ht="17" spans="1:8">
+    <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
         <v>10005</v>
       </c>
@@ -2476,7 +2599,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="17" spans="1:8">
+    <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
         <v>10006</v>
       </c>
@@ -2502,7 +2625,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="17" spans="1:8">
+    <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
         <v>10007</v>
       </c>
@@ -2528,7 +2651,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" customFormat="1" ht="17" spans="1:8">
+    <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
         <v>10008</v>
       </c>
@@ -2554,7 +2677,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" customFormat="1" ht="17" spans="1:8">
+    <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
         <v>10009</v>
       </c>
@@ -2580,7 +2703,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="17" spans="1:8">
+    <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
         <v>10010</v>
       </c>
@@ -2606,7 +2729,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="17" spans="1:8">
+    <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
         <v>10011</v>
       </c>
@@ -2632,7 +2755,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="17" spans="1:8">
+    <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
         <v>10012</v>
       </c>
@@ -2658,7 +2781,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="17" spans="1:8">
+    <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
         <v>10013</v>
       </c>
@@ -2684,7 +2807,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="17" spans="1:8">
+    <row r="40" customFormat="1" spans="1:8">
       <c r="A40">
         <v>10014</v>
       </c>
@@ -2710,7 +2833,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="17" spans="1:8">
+    <row r="41" customFormat="1" spans="1:8">
       <c r="A41">
         <v>10015</v>
       </c>
@@ -2736,7 +2859,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="17" spans="1:8">
+    <row r="42" customFormat="1" spans="1:8">
       <c r="A42">
         <v>10016</v>
       </c>
@@ -2762,7 +2885,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="17" spans="1:8">
+    <row r="43" customFormat="1" spans="1:8">
       <c r="A43">
         <v>10017</v>
       </c>
@@ -2788,7 +2911,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="17" spans="1:8">
+    <row r="44" customFormat="1" spans="1:8">
       <c r="A44">
         <v>10018</v>
       </c>
@@ -2814,7 +2937,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="17" spans="1:8">
+    <row r="45" customFormat="1" spans="1:8">
       <c r="A45">
         <v>10019</v>
       </c>
@@ -2840,7 +2963,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="17" spans="1:8">
+    <row r="46" customFormat="1" spans="1:8">
       <c r="A46">
         <v>10020</v>
       </c>
@@ -2866,7 +2989,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="17" spans="1:8">
+    <row r="47" customFormat="1" spans="1:8">
       <c r="A47">
         <v>10021</v>
       </c>
@@ -2892,7 +3015,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="17" spans="1:8">
+    <row r="48" customFormat="1" spans="1:8">
       <c r="A48">
         <v>10022</v>
       </c>
@@ -2918,7 +3041,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="17" spans="1:8">
+    <row r="49" customFormat="1" spans="1:8">
       <c r="A49">
         <v>10023</v>
       </c>
@@ -2944,7 +3067,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="17" spans="1:8">
+    <row r="50" customFormat="1" spans="1:8">
       <c r="A50">
         <v>10024</v>
       </c>
@@ -2970,7 +3093,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="34" spans="1:8">
+    <row r="51" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A51">
         <v>10025</v>
       </c>
@@ -2996,7 +3119,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="34" spans="1:8">
+    <row r="52" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A52">
         <v>10026</v>
       </c>
@@ -3022,446 +3145,732 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" s="2" customFormat="1" ht="17" spans="1:8">
+    <row r="53" s="2" customFormat="1" spans="1:8">
       <c r="A53" s="2">
         <v>20001</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>181</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="17" spans="1:8">
-      <c r="A54" s="1">
+    <row r="54" s="1" customFormat="1" spans="1:8">
+      <c r="A54" s="2">
+        <v>20002</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:8">
+      <c r="A55" s="2">
+        <v>20003</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:8">
+      <c r="A56" s="2">
+        <v>20004</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:8">
+      <c r="A57" s="2">
+        <v>20005</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:8">
+      <c r="A58" s="2">
+        <v>20006</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:8">
+      <c r="A59" s="2">
+        <v>20007</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:8">
+      <c r="A60" s="2">
+        <v>20008</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:8">
+      <c r="A61" s="2">
+        <v>20009</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:8">
+      <c r="A62" s="2">
+        <v>20010</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:8">
+      <c r="A63" s="2">
+        <v>20011</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:8">
+      <c r="A64" s="2">
+        <v>20012</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:8">
+      <c r="A65" s="1">
         <v>30001</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D54" s="1">
+      <c r="B65" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" s="1">
         <v>10</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="H54" s="7" t="s">
+      <c r="E65" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" ht="17" spans="1:8">
-      <c r="A55">
+    <row r="66" spans="1:8">
+      <c r="A66">
         <v>40001</v>
       </c>
-      <c r="B55" t="s">
-        <v>190</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>192</v>
-      </c>
-      <c r="F55" t="s">
-        <v>193</v>
-      </c>
-      <c r="G55" t="s">
-        <v>194</v>
-      </c>
-      <c r="H55" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="56" ht="17" spans="1:8">
-      <c r="A56">
-        <v>40002</v>
-      </c>
-      <c r="B56" t="s">
-        <v>196</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>198</v>
-      </c>
-      <c r="F56" t="s">
-        <v>199</v>
-      </c>
-      <c r="G56" t="s">
-        <v>194</v>
-      </c>
-      <c r="H56" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57" ht="17" spans="1:8">
-      <c r="A57">
-        <v>40003</v>
-      </c>
-      <c r="B57" t="s">
-        <v>201</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" t="s">
-        <v>203</v>
-      </c>
-      <c r="F57" t="s">
-        <v>204</v>
-      </c>
-      <c r="G57" t="s">
-        <v>194</v>
-      </c>
-      <c r="H57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" ht="17" spans="1:8">
-      <c r="A58">
-        <v>40004</v>
-      </c>
-      <c r="B58" t="s">
-        <v>205</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>207</v>
-      </c>
-      <c r="F58" t="s">
-        <v>208</v>
-      </c>
-      <c r="G58" t="s">
-        <v>194</v>
-      </c>
-      <c r="H58" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="59" ht="34" spans="1:8">
-      <c r="A59">
-        <v>40005</v>
-      </c>
-      <c r="B59" t="s">
-        <v>209</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>211</v>
-      </c>
-      <c r="F59" t="s">
-        <v>212</v>
-      </c>
-      <c r="G59" t="s">
-        <v>194</v>
-      </c>
-      <c r="H59" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="60" ht="17" spans="1:8">
-      <c r="A60">
-        <v>40006</v>
-      </c>
-      <c r="B60" t="s">
-        <v>213</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>214</v>
-      </c>
-      <c r="F60" t="s">
-        <v>215</v>
-      </c>
-      <c r="G60" t="s">
-        <v>216</v>
-      </c>
-      <c r="H60" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61" ht="17" spans="1:8">
-      <c r="A61">
-        <v>40007</v>
-      </c>
-      <c r="B61" t="s">
-        <v>217</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>218</v>
-      </c>
-      <c r="F61" t="s">
-        <v>219</v>
-      </c>
-      <c r="G61" t="s">
-        <v>216</v>
-      </c>
-      <c r="H61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="62" ht="17" spans="1:8">
-      <c r="A62">
-        <v>40008</v>
-      </c>
-      <c r="B62" t="s">
-        <v>220</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>221</v>
-      </c>
-      <c r="F62" t="s">
-        <v>222</v>
-      </c>
-      <c r="G62" t="s">
-        <v>216</v>
-      </c>
-      <c r="H62" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63" ht="17" spans="1:8">
-      <c r="A63">
-        <v>40009</v>
-      </c>
-      <c r="B63" t="s">
-        <v>223</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>224</v>
-      </c>
-      <c r="F63" t="s">
-        <v>225</v>
-      </c>
-      <c r="G63" t="s">
-        <v>216</v>
-      </c>
-      <c r="H63" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="64" ht="17" spans="1:8">
-      <c r="A64">
-        <v>40010</v>
-      </c>
-      <c r="B64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
-        <v>227</v>
-      </c>
-      <c r="F64" t="s">
-        <v>228</v>
-      </c>
-      <c r="G64" t="s">
-        <v>216</v>
-      </c>
-      <c r="H64" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="65" ht="17" spans="1:8">
-      <c r="A65">
-        <v>40011</v>
-      </c>
-      <c r="B65" t="s">
-        <v>229</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
-        <v>230</v>
-      </c>
-      <c r="F65" t="s">
-        <v>231</v>
-      </c>
-      <c r="G65" t="s">
-        <v>216</v>
-      </c>
-      <c r="H65" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" ht="17" spans="1:8">
-      <c r="A66">
-        <v>40012</v>
-      </c>
       <c r="B66" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F66" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="H66" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="67" ht="17" spans="1:8">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67">
-        <v>40013</v>
+        <v>40002</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="H67" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="68" ht="17" spans="1:8">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68">
-        <v>40014</v>
+        <v>40003</v>
       </c>
       <c r="B68" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68" t="s">
+        <v>247</v>
+      </c>
+      <c r="F68" t="s">
+        <v>248</v>
+      </c>
+      <c r="G68" t="s">
+        <v>238</v>
+      </c>
+      <c r="H68" t="s">
         <v>239</v>
       </c>
-      <c r="F68" t="s">
-        <v>240</v>
-      </c>
-      <c r="G68" t="s">
-        <v>216</v>
-      </c>
-      <c r="H68" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="69" ht="17" spans="1:8">
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69">
-        <v>40015</v>
+        <v>40004</v>
       </c>
       <c r="B69" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F69" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="G69" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="H69" t="s">
-        <v>200</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>40005</v>
+      </c>
+      <c r="B70" t="s">
+        <v>253</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>255</v>
+      </c>
+      <c r="F70" t="s">
+        <v>256</v>
+      </c>
+      <c r="G70" t="s">
+        <v>238</v>
+      </c>
+      <c r="H70" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>40006</v>
+      </c>
+      <c r="B71" t="s">
+        <v>257</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>258</v>
+      </c>
+      <c r="F71" t="s">
+        <v>259</v>
+      </c>
+      <c r="G71" t="s">
+        <v>260</v>
+      </c>
+      <c r="H71" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>40007</v>
+      </c>
+      <c r="B72" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>262</v>
+      </c>
+      <c r="F72" t="s">
+        <v>263</v>
+      </c>
+      <c r="G72" t="s">
+        <v>260</v>
+      </c>
+      <c r="H72" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>40008</v>
+      </c>
+      <c r="B73" t="s">
+        <v>264</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>265</v>
+      </c>
+      <c r="F73" t="s">
+        <v>266</v>
+      </c>
+      <c r="G73" t="s">
+        <v>260</v>
+      </c>
+      <c r="H73" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>40009</v>
+      </c>
+      <c r="B74" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>268</v>
+      </c>
+      <c r="F74" t="s">
+        <v>269</v>
+      </c>
+      <c r="G74" t="s">
+        <v>260</v>
+      </c>
+      <c r="H74" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>40010</v>
+      </c>
+      <c r="B75" t="s">
+        <v>270</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>271</v>
+      </c>
+      <c r="F75" t="s">
+        <v>272</v>
+      </c>
+      <c r="G75" t="s">
+        <v>260</v>
+      </c>
+      <c r="H75" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>40011</v>
+      </c>
+      <c r="B76" t="s">
+        <v>273</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>274</v>
+      </c>
+      <c r="F76" t="s">
+        <v>275</v>
+      </c>
+      <c r="G76" t="s">
+        <v>260</v>
+      </c>
+      <c r="H76" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>40012</v>
+      </c>
+      <c r="B77" t="s">
+        <v>276</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>277</v>
+      </c>
+      <c r="F77" t="s">
+        <v>278</v>
+      </c>
+      <c r="G77" t="s">
+        <v>260</v>
+      </c>
+      <c r="H77" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>40013</v>
+      </c>
+      <c r="B78" t="s">
+        <v>279</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>280</v>
+      </c>
+      <c r="F78" t="s">
+        <v>281</v>
+      </c>
+      <c r="G78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H78" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>40014</v>
+      </c>
+      <c r="B79" t="s">
+        <v>282</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>283</v>
+      </c>
+      <c r="F79" t="s">
+        <v>284</v>
+      </c>
+      <c r="G79" t="s">
+        <v>260</v>
+      </c>
+      <c r="H79" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>40015</v>
+      </c>
+      <c r="B80" t="s">
+        <v>285</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>286</v>
+      </c>
+      <c r="F80" t="s">
+        <v>287</v>
+      </c>
+      <c r="G80" t="s">
+        <v>260</v>
+      </c>
+      <c r="H80" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2064,18 +2064,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K80"/>
-  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.1759259259259" customWidth="1"/>
-    <col min="2" max="2" width="17.3055555555556" customWidth="1"/>
-    <col min="3" max="3" width="24.037037037037" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.9907407407407" customWidth="1"/>
-    <col min="5" max="5" width="28.212962962963" customWidth="1"/>
-    <col min="6" max="6" width="32.3611111111111" customWidth="1"/>
-    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="12.175" customWidth="1"/>
+    <col min="2" max="2" width="17.3083333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.0333333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.9916666666667" customWidth="1"/>
+    <col min="5" max="5" width="28.2166666666667" customWidth="1"/>
+    <col min="6" max="6" width="32.3583333333333" customWidth="1"/>
+    <col min="7" max="7" width="26.4416666666667" customWidth="1"/>
     <col min="8" max="8" width="15.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="13.6111111111111" customWidth="1"/>
-    <col min="10" max="10" width="15.8518518518519" customWidth="1"/>
+    <col min="9" max="9" width="13.6083333333333" customWidth="1"/>
+    <col min="10" max="10" width="15.85" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3093,7 +3093,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="51" s="1" customFormat="1" ht="27" spans="1:8">
       <c r="A51">
         <v>10025</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="52" s="1" customFormat="1" ht="27" spans="1:8">
       <c r="A52">
         <v>10026</v>
       </c>

--- a/Excel/ResData.xlsx
+++ b/Excel/ResData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="292">
   <si>
     <t>int</t>
   </si>
@@ -249,6 +249,18 @@
   </si>
   <si>
     <t>ArtRes/UI/Panel/SettingPanel</t>
+  </si>
+  <si>
+    <t>GameWinPanel</t>
+  </si>
+  <si>
+    <t>通关面板</t>
+  </si>
+  <si>
+    <t>UI/Panel/GameWinPanel</t>
+  </si>
+  <si>
+    <t>ArtRes/UI/Panel/GameWinPanel</t>
   </si>
   <si>
     <t>Ball</t>
@@ -2063,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.175" customWidth="1"/>
@@ -2469,9 +2481,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>10001</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
         <v>74</v>
@@ -2480,7 +2492,7 @@
         <v>75</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
         <v>76</v>
@@ -2489,41 +2501,41 @@
         <v>77</v>
       </c>
       <c r="G27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>10001</v>
+      </c>
+      <c r="B28" t="s">
         <v>78</v>
       </c>
-      <c r="H27" t="s">
+      <c r="C28" s="3" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:8">
-      <c r="A28">
-        <v>10002</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s">
         <v>82</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>83</v>
-      </c>
-      <c r="G28" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B29" t="s">
         <v>84</v>
@@ -2541,15 +2553,15 @@
         <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
@@ -2567,15 +2579,15 @@
         <v>91</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="B31" t="s">
         <v>92</v>
@@ -2593,15 +2605,15 @@
         <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="B32" t="s">
         <v>96</v>
@@ -2619,15 +2631,15 @@
         <v>99</v>
       </c>
       <c r="G32" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="B33" t="s">
         <v>100</v>
@@ -2645,15 +2657,15 @@
         <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="B34" t="s">
         <v>104</v>
@@ -2671,15 +2683,15 @@
         <v>107</v>
       </c>
       <c r="G34" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="B35" t="s">
         <v>108</v>
@@ -2697,15 +2709,15 @@
         <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="B36" t="s">
         <v>112</v>
@@ -2723,15 +2735,15 @@
         <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="B37" t="s">
         <v>116</v>
@@ -2749,15 +2761,15 @@
         <v>119</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="B38" t="s">
         <v>120</v>
@@ -2775,15 +2787,15 @@
         <v>123</v>
       </c>
       <c r="G38" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="B39" t="s">
         <v>124</v>
@@ -2801,15 +2813,15 @@
         <v>127</v>
       </c>
       <c r="G39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:8">
       <c r="A40">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="B40" t="s">
         <v>128</v>
@@ -2827,15 +2839,15 @@
         <v>131</v>
       </c>
       <c r="G40" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:8">
       <c r="A41">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="B41" t="s">
         <v>132</v>
@@ -2853,15 +2865,15 @@
         <v>135</v>
       </c>
       <c r="G41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="B42" t="s">
         <v>136</v>
@@ -2879,15 +2891,15 @@
         <v>139</v>
       </c>
       <c r="G42" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -2905,15 +2917,15 @@
         <v>143</v>
       </c>
       <c r="G43" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:8">
       <c r="A44">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="B44" t="s">
         <v>144</v>
@@ -2931,15 +2943,15 @@
         <v>147</v>
       </c>
       <c r="G44" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:8">
       <c r="A45">
-        <v>10019</v>
+        <v>10018</v>
       </c>
       <c r="B45" t="s">
         <v>148</v>
@@ -2957,15 +2969,15 @@
         <v>151</v>
       </c>
       <c r="G45" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:8">
       <c r="A46">
-        <v>10020</v>
+        <v>10019</v>
       </c>
       <c r="B46" t="s">
         <v>152</v>
@@ -2983,15 +2995,15 @@
         <v>155</v>
       </c>
       <c r="G46" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:8">
       <c r="A47">
-        <v>10021</v>
+        <v>10020</v>
       </c>
       <c r="B47" t="s">
         <v>156</v>
@@ -3009,15 +3021,15 @@
         <v>159</v>
       </c>
       <c r="G47" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="B48" t="s">
         <v>160</v>
@@ -3035,15 +3047,15 @@
         <v>163</v>
       </c>
       <c r="G48" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49">
-        <v>10023</v>
+        <v>10022</v>
       </c>
       <c r="B49" t="s">
         <v>164</v>
@@ -3061,15 +3073,15 @@
         <v>167</v>
       </c>
       <c r="G49" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:8">
       <c r="A50">
-        <v>10024</v>
+        <v>10023</v>
       </c>
       <c r="B50" t="s">
         <v>168</v>
@@ -3087,15 +3099,15 @@
         <v>171</v>
       </c>
       <c r="G50" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="27" spans="1:8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:8">
       <c r="A51">
-        <v>10025</v>
+        <v>10024</v>
       </c>
       <c r="B51" t="s">
         <v>172</v>
@@ -3113,15 +3125,15 @@
         <v>175</v>
       </c>
       <c r="G51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="27" spans="1:8">
       <c r="A52">
-        <v>10026</v>
+        <v>10025</v>
       </c>
       <c r="B52" t="s">
         <v>176</v>
@@ -3139,59 +3151,59 @@
         <v>179</v>
       </c>
       <c r="G52" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" spans="1:8">
-      <c r="A53" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="27" spans="1:8">
+      <c r="A53">
+        <v>10026</v>
+      </c>
+      <c r="B53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D53">
+        <v>6</v>
+      </c>
+      <c r="E53" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" t="s">
+        <v>183</v>
+      </c>
+      <c r="G53" t="s">
+        <v>82</v>
+      </c>
+      <c r="H53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" spans="1:8">
+      <c r="A54" s="2">
         <v>20001</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:8">
-      <c r="A54" s="2">
-        <v>20002</v>
-      </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>45</v>
@@ -3199,7 +3211,7 @@
     </row>
     <row r="55" s="1" customFormat="1" spans="1:8">
       <c r="A55" s="2">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>189</v>
@@ -3217,7 +3229,7 @@
         <v>192</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>45</v>
@@ -3225,7 +3237,7 @@
     </row>
     <row r="56" s="1" customFormat="1" spans="1:8">
       <c r="A56" s="2">
-        <v>20004</v>
+        <v>20003</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>193</v>
@@ -3243,7 +3255,7 @@
         <v>196</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>45</v>
@@ -3251,7 +3263,7 @@
     </row>
     <row r="57" s="1" customFormat="1" spans="1:8">
       <c r="A57" s="2">
-        <v>20005</v>
+        <v>20004</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>197</v>
@@ -3269,7 +3281,7 @@
         <v>200</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>45</v>
@@ -3277,7 +3289,7 @@
     </row>
     <row r="58" s="1" customFormat="1" spans="1:8">
       <c r="A58" s="2">
-        <v>20006</v>
+        <v>20005</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>201</v>
@@ -3295,7 +3307,7 @@
         <v>204</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>45</v>
@@ -3303,7 +3315,7 @@
     </row>
     <row r="59" s="1" customFormat="1" spans="1:8">
       <c r="A59" s="2">
-        <v>20007</v>
+        <v>20006</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>205</v>
@@ -3321,7 +3333,7 @@
         <v>208</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>45</v>
@@ -3329,7 +3341,7 @@
     </row>
     <row r="60" s="1" customFormat="1" spans="1:8">
       <c r="A60" s="2">
-        <v>20008</v>
+        <v>20007</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>209</v>
@@ -3347,7 +3359,7 @@
         <v>212</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>45</v>
@@ -3355,7 +3367,7 @@
     </row>
     <row r="61" s="1" customFormat="1" spans="1:8">
       <c r="A61" s="2">
-        <v>20009</v>
+        <v>20008</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>213</v>
@@ -3373,7 +3385,7 @@
         <v>216</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>45</v>
@@ -3381,7 +3393,7 @@
     </row>
     <row r="62" s="1" customFormat="1" spans="1:8">
       <c r="A62" s="2">
-        <v>20010</v>
+        <v>20009</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>217</v>
@@ -3399,7 +3411,7 @@
         <v>220</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>45</v>
@@ -3407,7 +3419,7 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="1:8">
       <c r="A63" s="2">
-        <v>20011</v>
+        <v>20010</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>221</v>
@@ -3425,7 +3437,7 @@
         <v>224</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>45</v>
@@ -3433,7 +3445,7 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="1:8">
       <c r="A64" s="2">
-        <v>20012</v>
+        <v>20011</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>225</v>
@@ -3451,119 +3463,119 @@
         <v>228</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:8">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
+        <v>20012</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:8">
+      <c r="A66" s="1">
         <v>30001</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="D65" s="1">
+      <c r="B66" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D66" s="1">
         <v>10</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H65" s="1" t="s">
+      <c r="E66" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66">
-        <v>40001</v>
-      </c>
-      <c r="B66" t="s">
-        <v>234</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>236</v>
-      </c>
-      <c r="F66" t="s">
-        <v>237</v>
-      </c>
-      <c r="G66" t="s">
-        <v>238</v>
-      </c>
-      <c r="H66" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>40002</v>
+        <v>40001</v>
       </c>
       <c r="B67" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67" t="s">
+        <v>240</v>
+      </c>
+      <c r="F67" t="s">
+        <v>241</v>
+      </c>
+      <c r="G67" t="s">
         <v>242</v>
       </c>
-      <c r="F67" t="s">
+      <c r="H67" t="s">
         <v>243</v>
-      </c>
-      <c r="G67" t="s">
-        <v>238</v>
-      </c>
-      <c r="H67" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>40003</v>
+        <v>40002</v>
       </c>
       <c r="B68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68" t="s">
+        <v>246</v>
+      </c>
+      <c r="F68" t="s">
         <v>247</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
+        <v>242</v>
+      </c>
+      <c r="H68" t="s">
         <v>248</v>
-      </c>
-      <c r="G68" t="s">
-        <v>238</v>
-      </c>
-      <c r="H68" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>40004</v>
+        <v>40003</v>
       </c>
       <c r="B69" t="s">
         <v>249</v>
@@ -3581,15 +3593,15 @@
         <v>252</v>
       </c>
       <c r="G69" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="H69" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>40005</v>
+        <v>40004</v>
       </c>
       <c r="B70" t="s">
         <v>253</v>
@@ -3607,41 +3619,41 @@
         <v>256</v>
       </c>
       <c r="G70" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="H70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>40006</v>
+        <v>40005</v>
       </c>
       <c r="B71" t="s">
         <v>257</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G71" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="H71" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>40007</v>
+        <v>40006</v>
       </c>
       <c r="B72" t="s">
         <v>261</v>
@@ -3659,218 +3671,244 @@
         <v>263</v>
       </c>
       <c r="G72" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H72" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>40008</v>
+        <v>40007</v>
       </c>
       <c r="B73" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G73" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H73" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>40009</v>
+        <v>40008</v>
       </c>
       <c r="B74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F74" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G74" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H74" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>40010</v>
+        <v>40009</v>
       </c>
       <c r="B75" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G75" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H75" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>40011</v>
+        <v>40010</v>
       </c>
       <c r="B76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G76" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H76" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>40012</v>
+        <v>40011</v>
       </c>
       <c r="B77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H77" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>40013</v>
+        <v>40012</v>
       </c>
       <c r="B78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F78" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G78" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H78" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>40014</v>
+        <v>40013</v>
       </c>
       <c r="B79" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G79" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H79" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>40015</v>
+        <v>40014</v>
       </c>
       <c r="B80" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F80" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G80" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H80" t="s">
-        <v>244</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81">
+        <v>40015</v>
+      </c>
+      <c r="B81" t="s">
+        <v>289</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>290</v>
+      </c>
+      <c r="F81" t="s">
+        <v>291</v>
+      </c>
+      <c r="G81" t="s">
+        <v>264</v>
+      </c>
+      <c r="H81" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
